--- a/spreadsheet/ajbell.xlsx
+++ b/spreadsheet/ajbell.xlsx
@@ -2469,9 +2469,14 @@
           <t>GB00BRBMZ190</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:1VET</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2486,9 +2491,14 @@
           <t>GB00BRBMZ190</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:1VET</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2503,9 +2513,14 @@
           <t>CH1199067674</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:CBTC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2520,9 +2535,14 @@
           <t>CH1199067674</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:CBTU</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2559,9 +2579,14 @@
           <t>CH0454664001</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:BTCU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2576,9 +2601,14 @@
           <t>CH1146882308</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:BOLD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2593,9 +2623,14 @@
           <t>CH1146882308</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:BOLU</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2610,9 +2645,14 @@
           <t>CH1209763130</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:ETHC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2649,9 +2689,14 @@
           <t>CH0454664027</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:AETH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2666,9 +2711,14 @@
           <t>CH0454664027</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:ETHU</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2683,9 +2733,14 @@
           <t>IE000J7QYHD8</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:ARAW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2700,9 +2755,14 @@
           <t>IE000GGQK173</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:AREG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account</t>
         </is>
       </c>
     </row>
@@ -2739,9 +2799,14 @@
           <t>US00326A1043</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:0IEE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2756,9 +2821,14 @@
           <t>IE00BKPTXQ89</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:MMLP</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2773,9 +2843,14 @@
           <t>IE00BKPTXQ89</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:PMLP</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -2790,9 +2865,14 @@
           <t>LU2785470191</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:FAAA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -2829,9 +2909,14 @@
           <t>LU2825557270</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:XAAA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2846,9 +2931,14 @@
           <t>LU0496786905</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:LAUU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -2863,9 +2953,14 @@
           <t>LU1829218749</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:COMG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2880,9 +2975,14 @@
           <t>LU1829218749</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:COMU</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -2919,9 +3019,14 @@
           <t>FR0010592014</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/CHIX:LVCP</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2936,9 +3041,14 @@
           <t>FR0007052782</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:CACX</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2953,9 +3063,14 @@
           <t>LU1931975079</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:PRIC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -2970,9 +3085,14 @@
           <t>LU2977997209</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:CBDG</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account</t>
         </is>
       </c>
     </row>
@@ -3009,9 +3129,14 @@
           <t>LU3206575048</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:GHYA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account</t>
         </is>
       </c>
     </row>
@@ -3026,9 +3151,14 @@
           <t>LU1437018598</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:MTXX</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -3043,9 +3173,14 @@
           <t>LU1681047236</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:0A3A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -3060,9 +3195,14 @@
           <t>LU1681047236</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:MSED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -3099,9 +3239,14 @@
           <t>LU3122198321</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:GBBD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account</t>
         </is>
       </c>
     </row>
@@ -3116,9 +3261,14 @@
           <t>LU2573967036</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:LEMA LN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -3133,9 +3283,14 @@
           <t>LU2573966905</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:U127</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -3150,9 +3305,14 @@
           <t>LU2573966905</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:E127</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -3189,9 +3349,14 @@
           <t>LU1781541252</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:LCJP</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -3206,9 +3371,14 @@
           <t>LU1781541252</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:LCJD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3223,9 +3393,14 @@
           <t>LU1781541682</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:LCJG</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -3240,9 +3415,14 @@
           <t>IE000IEGVMH6</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:MSCU</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account</t>
         </is>
       </c>
     </row>
@@ -3279,9 +3459,14 @@
           <t>IE000BI8OT95</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:MWRU</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account</t>
         </is>
       </c>
     </row>
@@ -3296,9 +3481,14 @@
           <t>LU1829221024</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:NASL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -3313,9 +3503,14 @@
           <t>LU1829221024</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:NASD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
       </c>
     </row>
@@ -3330,9 +3525,14 @@
           <t>LU1135865084</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:SP5L</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
       </c>
     </row>
@@ -7140,55 +7340,55 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" display="https://www.ajbell.co.uk/market-research/LSE:1VBS" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" display="https://www.ajbell.co.uk/market-research/LSE:1VET" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="https://www.ajbell.co.uk/market-research/LSE:1VET" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="https://www.ajbell.co.uk/market-research/LSE:CBTC" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="https://www.ajbell.co.uk/market-research/LSE:CBTU" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="https://www.ajbell.co.uk/market-research/LSE:ABTC" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="https://www.ajbell.co.uk/market-research/LSE:BTCU" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="https://www.ajbell.co.uk/market-research/LSE:BOLD" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" display="https://www.ajbell.co.uk/market-research/LSE:BOLU" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" display="https://www.ajbell.co.uk/market-research/LSE:ETHC" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="https://www.ajbell.co.uk/market-research/LSE:CETU" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="https://www.ajbell.co.uk/market-research/LSE:AETH" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" display="https://www.ajbell.co.uk/market-research/LSE:ETHU" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="https://www.ajbell.co.uk/market-research/LSE:ARAW" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" display="https://www.ajbell.co.uk/market-research/LSE:AREG" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" display="https://www.ajbell.co.uk/market-research/LSE:ASCH" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" display="https://www.ajbell.co.uk/market-research/LSE:0IEE" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" display="https://www.ajbell.co.uk/market-research/LSE:MMLP" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" display="https://www.ajbell.co.uk/market-research/LSE:PMLP" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" display="https://www.ajbell.co.uk/market-research/LSE:FAAA" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" display="https://www.ajbell.co.uk/market-research/LSE:AAAG" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" display="https://www.ajbell.co.uk/market-research/LSE:XAAA" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" display="https://www.ajbell.co.uk/market-research/LSE:LAUU" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" display="https://www.ajbell.co.uk/market-research/LSE:COMG" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" display="https://www.ajbell.co.uk/market-research/LSE:COMU" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" display="https://www.ajbell.co.uk/market-research/XPAR:LVC" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" display="https://www.ajbell.co.uk/market-research/CHIX:LVCP" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" display="https://www.ajbell.co.uk/market-research/LSE:CACX" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" display="https://www.ajbell.co.uk/market-research/LSE:PRIC" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" display="https://www.ajbell.co.uk/market-research/LSE:CBDG" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" display="https://www.ajbell.co.uk/market-research/LSE:CBDU" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" display="https://www.ajbell.co.uk/market-research/LSE:GHYA" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" display="https://www.ajbell.co.uk/market-research/LSE:MTXX" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" display="https://www.ajbell.co.uk/market-research/LSE:0A3A" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" display="https://www.ajbell.co.uk/market-research/LSE:MSED" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" display="https://www.ajbell.co.uk/market-research/LSE:C50U" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" display="https://www.ajbell.co.uk/market-research/LSE:GBBD" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" display="https://www.ajbell.co.uk/market-research/LSE:LEMA LN" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" display="https://www.ajbell.co.uk/market-research/LSE:U127" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" display="https://www.ajbell.co.uk/market-research/LSE:E127" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" display="https://www.ajbell.co.uk/market-research/LSE:MFEX" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" display="https://www.ajbell.co.uk/market-research/LSE:LCJP" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" display="https://www.ajbell.co.uk/market-research/LSE:LCJD" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" display="https://www.ajbell.co.uk/market-research/LSE:LCJG" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" display="https://www.ajbell.co.uk/market-research/LSE:MSCU" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" display="https://www.ajbell.co.uk/market-research/LSE:MWRL" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" display="https://www.ajbell.co.uk/market-research/LSE:MWRU" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" display="https://www.ajbell.co.uk/market-research/LSE:NASL" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" display="https://www.ajbell.co.uk/market-research/LSE:NASD" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" display="https://www.ajbell.co.uk/market-research/LSE:SP5L" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/spreadsheet/ajbell.xlsx
+++ b/spreadsheet/ajbell.xlsx
@@ -2474,7 +2474,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:1VET</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2496,7 +2496,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:1VET</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2518,7 +2518,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:CBTC</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, SIPP and Dividend reinvestment</t>
         </is>
@@ -2540,7 +2540,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:CBTU</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2584,7 +2584,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:BTCU</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2606,7 +2606,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:BOLD</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, SIPP and Dividend reinvestment</t>
         </is>
@@ -2628,7 +2628,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:BOLU</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2650,7 +2650,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:ETHC</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, SIPP and Dividend reinvestment</t>
         </is>
@@ -2694,7 +2694,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:AETH</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2716,7 +2716,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:ETHU</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2738,7 +2738,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:ARAW</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -2760,7 +2760,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:AREG</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account</t>
         </is>
@@ -2804,7 +2804,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:0IEE</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
@@ -2826,7 +2826,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:MMLP</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
@@ -2848,7 +2848,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:PMLP</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -2870,7 +2870,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:FAAA</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -2914,7 +2914,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:XAAA</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, SIPP and Dividend reinvestment</t>
         </is>
@@ -2936,7 +2936,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:LAUU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -2958,7 +2958,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:COMG</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -2980,7 +2980,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:COMU</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -3024,7 +3024,7 @@
           <t>https://www.ajbell.co.uk/market-research/CHIX:LVCP</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3046,7 +3046,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:CACX</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -3068,7 +3068,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:PRIC</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
@@ -3090,7 +3090,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:CBDG</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account</t>
         </is>
@@ -3134,7 +3134,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:GHYA</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account</t>
         </is>
@@ -3156,7 +3156,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:MTXX</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
@@ -3178,7 +3178,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:0A3A</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -3200,7 +3200,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:MSED</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP and Dividend reinvestment</t>
         </is>
@@ -3244,7 +3244,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:GBBD</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account</t>
         </is>
@@ -3266,7 +3266,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:LEMA LN</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -3288,7 +3288,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:U127</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -3310,7 +3310,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:E127</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -3354,7 +3354,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:LCJP</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -3376,7 +3376,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:LCJD</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3398,7 +3398,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:LCJG</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -3420,7 +3420,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:MSCU</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:MWRU</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account</t>
         </is>
@@ -3486,7 +3486,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:NASL</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>
@@ -3508,7 +3508,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:NASD</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA and SIPP</t>
         </is>
@@ -3530,7 +3530,7 @@
           <t>https://www.ajbell.co.uk/market-research/LSE:SP5L</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>This share can be held in a Dealing account, Stocks and shares ISA, Lifetime ISA, JISA, SIPP, Regular investment and Dividend reinvestment</t>
         </is>

--- a/spreadsheet/ajbell.xlsx
+++ b/spreadsheet/ajbell.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D312"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.47265625" defaultRowHeight="18" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="45.53" customWidth="1" style="9" min="1" max="1"/>
@@ -465,7 +465,7 @@
           <t>GB00B1YW4409</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:III</t>
         </is>
@@ -575,7 +575,7 @@
           <t>GB0006048770</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:ANII</t>
         </is>
@@ -685,7 +685,7 @@
           <t>GB00BD9PXH49</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:ASLI</t>
         </is>
@@ -795,7 +795,7 @@
           <t>KYG012921535</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:AOF</t>
         </is>
@@ -905,7 +905,7 @@
           <t>GB00B1VS7G47</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:ALNA</t>
         </is>
@@ -1015,7 +1015,7 @@
           <t>GG00BQKNKR70</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:AA4</t>
         </is>
@@ -1125,7 +1125,7 @@
           <t>GB00BF50VS41</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:AIE</t>
         </is>
@@ -1235,7 +1235,7 @@
           <t>GB00BLH3CY60</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:AGT</t>
         </is>
@@ -1345,7 +1345,7 @@
           <t>GB00BFXYH242</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>https://www.ajbell.co.uk/market-research/LSE:BGS</t>
         </is>
@@ -1555,831 +1555,4927 @@
       </c>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C52" s="15" t="n"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BH Macro USD Ord</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GG00BQBFY479</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BHMU</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C53" s="15" t="n"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BioPharma Credit Ord</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GB00BDGKMY29</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BPCR</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C54" s="15" t="n"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BlackFinch Spring VCT Ord</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GB00BKV46W45</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BFSP</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C55" s="15" t="n"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BlackRock American Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GB00B7W0XJ61</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRAI</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C56" s="15" t="n"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BlackRock Energy and Resources Inc</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GB00B0N8MF98</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BERI</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C57" s="15" t="n"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BlackRock Frontiers Ord</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GB00B3SXM832</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRFI</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C58" s="15" t="n"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BlackRock Greater Europe Ord</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GB00B01RDH75</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRGE</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C59" s="15" t="n"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BlackRock Income and Growth Ord</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GB0030961691</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRIG</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C60" s="15" t="n"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BlackRock Latin American Ord</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GB0005058408</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRLA</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C61" s="15" t="n"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BlackRock Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GB0006436108</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRSC</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C62" s="15" t="n"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BlackRock World Mining Trust Ord</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GB0005774855</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BRWM</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C63" s="15" t="n"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Bluefield Solar Income Fund</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GG00BB0RDB98</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BSIF</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C64" s="15" t="n"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>British&amp;American 2025 3.5%</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BAFV</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C65" s="15" t="n"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>British &amp; American Ord</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GB0000653112</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BAF</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C66" s="15" t="n"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>British Smaller Companies VCT Ord</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GB0001403152</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BSV</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C67" s="15" t="n"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>British Smaller Companies VCT2 Ord</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GB0005001796</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BSC</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C68" s="15" t="n"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Brown Advisory US Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GB0003463402</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BASC</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C69" s="15" t="n"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Brunner Ord</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GB0001490001</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BUT</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C70" s="15" t="n"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Calculus VCT Ord</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GB00BYQPF348</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CLC</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C71" s="15" t="n"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Caledonia Investments Ord</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GB00BTNQ8K38</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CLDN</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C72" s="15" t="n"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Canadian General Investments Ord</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CA1358251074</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/TSX:CGI</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C73" s="15" t="n"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Canadian General Investments Ord GBP</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CA1358251074</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CGI</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C74" s="15" t="n"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Capital Gearing Ord</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GB0001738615</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CGT</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C75" s="15" t="n"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Castelnau Group Ord</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GG00BMWWJM28</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CGL</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C76" s="15" t="n"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CC Japan Income &amp; Growth Ord</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GB00BYSRMH16</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CCJI</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C77" s="15" t="n"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ceiba Investments Ord</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GG00BFMDJH11</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CBA</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C78" s="15" t="n"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chelverton UK Dividend Trust Ord</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GB0006615826</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SDV</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C79" s="15" t="n"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chenavari Toro Income Fund Ord</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GG00BWBSDM98</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TORO</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C80" s="15" t="n"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chrysalis Investments Limited Ord</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GG00BGJYPP46</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CHRY</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C81" s="15" t="n"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cordiant Digital Infrastructure S Share</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GG00BMDGQT90</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CSRD</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C82" s="15" t="n"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cordiant Digital Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GG00BMC7TM77</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CORD</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C83" s="15" t="n"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CQS Natural Resources G&amp;I Ord</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GB0000353929</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CYN</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C84" s="15" t="n"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CQS New City High Yield Ord</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JE00B1LZS514</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NCYF</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C85" s="15" t="n"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Crystal Amber Ord</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GG00B1Z2SL48</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CRS</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C86" s="15" t="n"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CT Global Managed Portfolio Growth Ord</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>GB00B2PP2527</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CMPG</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C87" s="15" t="n"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CT Global Managed Portfolio Income Ord</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GB00B2PP3J36</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CMPI</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C88" s="15" t="n"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CT Healthcare Trust plc</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GB00BZCNLL95</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CTHT</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C89" s="15" t="n"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CT Private Equity Trust Ord</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GB0030738271</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CTPE</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C90" s="15" t="n"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CT UK Capital and Income Ord</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GB0003463287</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CTUK</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C91" s="15" t="n"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CT UK High Income Ord</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GB00B1N4G299</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CHI</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C92" s="15" t="n"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CT UK High Income B Share Ord</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GB00B1N4H594</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CHIB</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C93" s="15" t="n"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Custodian Property Income REIT Ord</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GB00BJFLFT45</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CREI</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C94" s="15" t="n"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CVC Income &amp; Growth EUR</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JE00B9G79F59</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CVCE</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C95" s="15" t="n"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CVC Income &amp; Growth GBP</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JE00B9MRHZ51</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CVCG</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C96" s="15" t="n"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DCI Advisors Limited Ord</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GG00BSWT8V72</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:DCI</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C97" s="15" t="n"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Develop North Ord</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GB00BD0ND667</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:DVNO</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C98" s="15" t="n"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Digital 9 Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>JE00BMDKH437</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:DGI9</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C99" s="15" t="n"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Diverse Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GB00B65TLW28</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:DIVI</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C100" s="15" t="n"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DP Aircraft I Ord</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GG00BBP6HP33</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:DPA</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C101" s="15" t="n"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Dunedin Income Growth Ord</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GB0003406096</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:DIG</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C102" s="15" t="n"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ecofin Global Utilities &amp; Infra Ord</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GB00BD3V4641</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:EGL</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C103" s="15" t="n"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ecofin US Renewables Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GB00BLPK4430</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RNEW</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C104" s="15" t="n"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Edinburgh Investment Ord</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GB0003052338</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:EDIN</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C105" s="15" t="n"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Edinburgh Worldwide Ord</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GB00BHSRZC82</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:EWI</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C106" s="15" t="n"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EJF Investments Ord</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>JE00BF0D1M25</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:EJFI</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C107" s="15" t="n"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EJF Investments ZDP 2029</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>JE00BRZSNL95</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:EJFZ</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C108" s="15" t="n"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>EPE Special Opportunities Ord</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BMG3163K1053</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ESO</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C109" s="15" t="n"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>European Opportunities Trust</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GB0000197722</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:EOT</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C110" s="15" t="n"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>F&amp;C Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GB0003466074</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FCIT</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C111" s="15" t="n"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Fair Oaks Income 2021 Ord</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GG00BNNLWT35</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FAIR</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C112" s="15" t="n"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Fair Oaks Income Realisation Shares</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GG00BSWVSD56</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FA17</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C113" s="15" t="n"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Fidelity Asian Values Ord</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GB0003322319</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FAS</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C114" s="15" t="n"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Fidelity China Special Situations Ord</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GB00B62Z3C74</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FCSS</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C115" s="15" t="n"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Fidelity Emerging Markets Ord</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GG00B4L0PD47</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FEML</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C116" s="15" t="n"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Fidelity European Trust Ord</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GB00BK1PKQ95</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FEV</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C117" s="15" t="n"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Fidelity Special Values Ord</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GB00BWXC7Y93</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FSV</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C118" s="15" t="n"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Finsbury Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GB0007816068</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FGT</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C119" s="15" t="n"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Foresight Enterprise VCT Ord</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GB00B07YBS95</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FTF</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C120" s="15" t="n"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Foresight Environmental Infra Ord</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>GG00BJL5FH87</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FGEN</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C121" s="15" t="n"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Foresight Solar Ord</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>JE00BD3QJR55</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FSFL</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C122" s="15" t="n"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Foresight Technology VCT</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GB00BKF2JH04</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FWT</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C123" s="15" t="n"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Foresight VCT Ord</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GB00B68K3716</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FTV</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C124" s="15" t="n"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Foresight Ventures VCT plc</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GB00BRBQ0C76</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FVEN</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C125" s="15" t="n"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Fuel Ventures VCT PLC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GB00BP2RHT10</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:FVV</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C126" s="15" t="n"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Gabelli Merchant Partners Ord</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GB00BD8P0741</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GMP</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C127" s="15" t="n"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GCP Asset Backed Income</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>JE00BPCSN748</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GABI</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C128" s="15" t="n"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GCP Infrastructure Investment Ord</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>JE00B6173J15</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GCP</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C129" s="15" t="n"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Geiger Counter Ord</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GB00B15FW330</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GCL</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C130" s="15" t="n"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Global Opportunities Trust Ord</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GB0033862573</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GOT</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C131" s="15" t="n"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Globalworth Real Estate Investments Ord</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>GG00B979FD04</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GWI</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C132" s="15" t="n"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Golden Prospect Precious Metal Ord</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>GG00B1G9T992</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GPM</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C133" s="15" t="n"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Gore Street Energy Storage Fund Ord</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GB00BG0P0V73</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GSF</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C134" s="15" t="n"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Greencoat Renewables</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IE00BF2NR112</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GRP</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C135" s="15" t="n"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Greencoat UK Wind</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GB00B8SC6K54</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:UKW</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C136" s="15" t="n"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Gresham House Energy Storage Ord</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GB00BFX3K770</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GRID</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C137" s="15" t="n"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Gresham House Income &amp; Growth 2 VCT Ord</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>GB00B01WL239</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GHV2</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C138" s="15" t="n"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Gresham House Income &amp; Growth VCT Ord</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GB00B29BN198</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GHV1</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C139" s="15" t="n"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Gresham House Renewable Energy VCT 1 Ord</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GB00B4M2G812</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GV1O</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C140" s="15" t="n"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Gresham House Renewable Energy VCT 2 Ord</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GB00B43GVJ82</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GV2O</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C141" s="15" t="n"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>GRIT Investment Trust plc</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>GB00BL594W83</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GRIT</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C142" s="15" t="n"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Ground Rents Income Fund Ord</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>GB00B715WG26</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GRIO</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C143" s="15" t="n"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guinness VCT Ord</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>GB00BQD0HG35</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GVCT</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C144" s="15" t="n"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Hansa Investment Company Ltd 'A' Class A</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BMG428941089</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HANA</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C145" s="15" t="n"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hansa Investment Company Ltd Ord</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BMG428941162</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HAN</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C146" s="15" t="n"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>HarbourVest Global Priv Equity Ord</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GG00BR30MJ80</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HVPE</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C147" s="15" t="n"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Hargreave Hale AIM VCT Ord</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>GB00B02WHS05</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HHV</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C148" s="15" t="n"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Henderson Far East Income Ord</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>JE00B1GXH751</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HFEL</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C149" s="15" t="n"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Henderson High Income Ord</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GB0009580571</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HHI</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C150" s="15" t="n"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Henderson Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>GB0009065060</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HSL</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C151" s="15" t="n"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Herald Ord</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>GB0004228648</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HRI</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C152" s="15" t="n"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>HgCapital Trust Ord</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>GB00BJ0LT190</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HGT</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C153" s="15" t="n"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>HICL Infrastructure PLC Ord</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>GB00BJLP1Y77</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HICL</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C154" s="15" t="n"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Home REIT Ord</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>GB00BJP5HK17</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HOME</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C155" s="15" t="n"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Hydrogen Capital Growth</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>GB00BL6K7L04</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HGEN</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C156" s="15" t="n"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ICG Enterprise Trust Ord</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>GB0003292009</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ICGT</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C157" s="15" t="n"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ICG-Longbow Senior Sec. UK Prop Debt Inv</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>GG00B8C23S81</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LBOW</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C158" s="15" t="n"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Impax Environmental Markets Ord</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>GB0031232498</t>
+        </is>
+      </c>
+      <c r="C158" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:IEM</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C159" s="15" t="n"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>India Capital Growth Ord</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>GB00B0P8RJ60</t>
+        </is>
+      </c>
+      <c r="C159" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:IGC</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C160" s="15" t="n"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>International Biotechnology Ord</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>GB0004559349</t>
+        </is>
+      </c>
+      <c r="C160" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:IBT</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C161" s="15" t="n"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>International Public Partnerships Ord</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>GB00B188SR50</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:INPP</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C162" s="15" t="n"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Intuitive Investments Group PLC Ord</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>GB00BPTH6Y20</t>
+        </is>
+      </c>
+      <c r="C162" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:IIG</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C163" s="15" t="n"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Invesco Asia Dragon Trust Ord</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>GB0004535307</t>
+        </is>
+      </c>
+      <c r="C163" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:IAD</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C164" s="15" t="n"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Invesco Bond Income Plus Ord</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>JE00B6RMDP68</t>
+        </is>
+      </c>
+      <c r="C164" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BIPS</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C165" s="15" t="n"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Invesco Global Equity Income Trust ord</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>GB00B1DQ6472</t>
+        </is>
+      </c>
+      <c r="C165" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:IGET</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C166" s="15" t="n"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Investment Company Ord</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>GB00BV4FKD05</t>
+        </is>
+      </c>
+      <c r="C166" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:INV</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C167" s="15" t="n"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>JPEL Private Equity Ord</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>GG00BVPBWF31</t>
+        </is>
+      </c>
+      <c r="C167" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JPEL</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C168" s="15" t="n"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>JPMorgan American Ord</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>GB00BKZGVH64</t>
+        </is>
+      </c>
+      <c r="C168" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JAM</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C169" s="15" t="n"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>JPMorgan Asia Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>GB0001320778</t>
+        </is>
+      </c>
+      <c r="C169" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JAGI</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C170" s="15" t="n"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>JPMorgan China Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>GB0003435012</t>
+        </is>
+      </c>
+      <c r="C170" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JCGI</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C171" s="15" t="n"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>JPMorgan Claverhouse Ord</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>GB0003422184</t>
+        </is>
+      </c>
+      <c r="C171" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JCH</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C172" s="15" t="n"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerg EMEA Sec Plc</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>GB0032164732</t>
+        </is>
+      </c>
+      <c r="C172" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JEMA</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C173" s="15" t="n"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Markets Div Inc</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GB00B5ZZY915</t>
+        </is>
+      </c>
+      <c r="C173" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JEMI</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C174" s="15" t="n"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Markets Growth &amp; Inc</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>GB00BMXWN182</t>
+        </is>
+      </c>
+      <c r="C174" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JMGI</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C175" s="15" t="n"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>JPMorgan European Discovery Ord</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>GB00BMTS0Z37</t>
+        </is>
+      </c>
+      <c r="C175" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JEDT</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C176" s="15" t="n"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>JPMorgan European Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>GB00BPR9Y246</t>
+        </is>
+      </c>
+      <c r="C176" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JEGI</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C177" s="15" t="n"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>JPMorgan Global Core Real Assets Ord</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>GG00BS5ZFX32</t>
+        </is>
+      </c>
+      <c r="C177" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JARA</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C178" s="15" t="n"/>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>JPMorgan Global Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>GB00BYMKY695</t>
+        </is>
+      </c>
+      <c r="C178" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JGGI</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C179" s="15" t="n"/>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>JPMorgan India Growth &amp; Income plc</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>GB0003450359</t>
+        </is>
+      </c>
+      <c r="C179" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JIGI</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C180" s="15" t="n"/>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>JPMorgan Japanese Ord</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>GB0001740025</t>
+        </is>
+      </c>
+      <c r="C180" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JFJ</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C181" s="15" t="n"/>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>JPMorgan UK Small Cap Growth &amp; Income</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>GB00BF7L8P11</t>
+        </is>
+      </c>
+      <c r="C181" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JUGI</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C182" s="15" t="n"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>JPMorgan US Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>GB00BJL5F346</t>
+        </is>
+      </c>
+      <c r="C182" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JUSC</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C183" s="15" t="n"/>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>JZ Capital Partners Ord</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>GG00BPNZ7G17</t>
+        </is>
+      </c>
+      <c r="C183" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:JZCP</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C184" s="15" t="n"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>KCR Residential REIT</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>GB00BYWK1Q82</t>
+        </is>
+      </c>
+      <c r="C184" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:KCR</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C185" s="15" t="n"/>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Law Debenture Corporation Ord</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>GB0031429219</t>
+        </is>
+      </c>
+      <c r="C185" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LWDB</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C186" s="15" t="n"/>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Life Science REIT Ord</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>GB00BP5X4Q29</t>
+        </is>
+      </c>
+      <c r="C186" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LABS</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C187" s="15" t="n"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Life Settlement Assets A Ord</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>GB00BF1Q4B05</t>
+        </is>
+      </c>
+      <c r="C187" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LSAA</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C188" s="15" t="n"/>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Lindsell Train Ord</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>GB00BNKDVV71</t>
+        </is>
+      </c>
+      <c r="C188" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LTI</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C189" s="15" t="n"/>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Literacy Capital PLC</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>GB00BMF1L080</t>
+        </is>
+      </c>
+      <c r="C189" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BOOK</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C190" s="15" t="n"/>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Livermore Investments Ord</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>VGG550931015</t>
+        </is>
+      </c>
+      <c r="C190" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LIV</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C191" s="15" t="n"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>LMS Capital Ord</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>GB00B12MHD28</t>
+        </is>
+      </c>
+      <c r="C191" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LMS</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C192" s="15" t="n"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Lowland Ord</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>GB00BNXGHS27</t>
+        </is>
+      </c>
+      <c r="C192" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:LWI</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C193" s="15" t="n"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>M&amp;G Credit Income Investment Ord</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>GB00BFYYL325</t>
+        </is>
+      </c>
+      <c r="C193" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MGCI</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C194" s="15" t="n"/>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Macau Property Opportunities Ord</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>GG00BGDYFV61</t>
+        </is>
+      </c>
+      <c r="C194" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MPO</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C195" s="15" t="n"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Majedie Investments Ord</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>GB0005555221</t>
+        </is>
+      </c>
+      <c r="C195" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MAJE</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C196" s="15" t="n"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Manchester &amp; London Ord</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>GB0002258472</t>
+        </is>
+      </c>
+      <c r="C196" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MNL</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C197" s="15" t="n"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Marwyn Value Investors 2016 Realisation</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>KYG5897M2326</t>
+        </is>
+      </c>
+      <c r="C197" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MVIR</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C198" s="15" t="n"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Marwyn Value Investors 2021 Realisation</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>KYG5897M2243</t>
+        </is>
+      </c>
+      <c r="C198" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MVR2</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C199" s="15" t="n"/>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Marwyn Value Investors Ord</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>KYG5897M1740</t>
+        </is>
+      </c>
+      <c r="C199" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MVI</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C200" s="15" t="n"/>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT Ord</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>GB0004122858</t>
+        </is>
+      </c>
+      <c r="C200" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MIG1</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C201" s="15" t="n"/>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT 3 Ord</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>GB0031153769</t>
+        </is>
+      </c>
+      <c r="C201" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MIG3</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C202" s="15" t="n"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT 4 Ord</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>GB00B043QW84</t>
+        </is>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MAV4</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C203" s="15" t="n"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Maven Income &amp; Growth VCT 5 Ord</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>GB0002057536</t>
+        </is>
+      </c>
+      <c r="C203" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MIG5</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C204" s="15" t="n"/>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Maven Renovar VCT Ord</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>GB00B641BB82</t>
+        </is>
+      </c>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MRV</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C205" s="15" t="n"/>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Mercantile Ord</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>GB00BF4JDH58</t>
+        </is>
+      </c>
+      <c r="C205" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MRC</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C206" s="15" t="n"/>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Mid Wynd International Inv Tr Ord</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>GB00B6VTTK07</t>
+        </is>
+      </c>
+      <c r="C206" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MWY</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C207" s="15" t="n"/>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>MIGO Opportunities Trust Ord</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>GB0034365949</t>
+        </is>
+      </c>
+      <c r="C207" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MIGO</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C208" s="15" t="n"/>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Mobius Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>GB00BFZ7R980</t>
+        </is>
+      </c>
+      <c r="C208" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MMIT</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C209" s="15" t="n"/>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Molten Ventures Ord</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>GB00BY7QYJ50</t>
+        </is>
+      </c>
+      <c r="C209" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GROW</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C210" s="15" t="n"/>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Molten Ventures VCT Ord</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>GB0002867140</t>
+        </is>
+      </c>
+      <c r="C210" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MVCT</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C211" s="15" t="n"/>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Monks Ord</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>GB0030517261</t>
+        </is>
+      </c>
+      <c r="C211" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MNKS</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C212" s="15" t="n"/>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Montanaro European Smaller Ord</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>GB00BM8H3X05</t>
+        </is>
+      </c>
+      <c r="C212" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MTE</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C213" s="15" t="n"/>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Montanaro UK Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>GB00BZ1H9L86</t>
+        </is>
+      </c>
+      <c r="C213" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MTU</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C214" s="15" t="n"/>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Murray Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>GB0006111123</t>
+        </is>
+      </c>
+      <c r="C214" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MUT</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C215" s="15" t="n"/>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Murray International Ord</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>GB00BQZCCB79</t>
+        </is>
+      </c>
+      <c r="C215" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MYI</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C216" s="15" t="n"/>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>NB Private Equity Partners Class A Ord</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>GG00B1ZBD492</t>
+        </is>
+      </c>
+      <c r="C216" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NBPE</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C217" s="15" t="n"/>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>New Star Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>GB0002631041</t>
+        </is>
+      </c>
+      <c r="C217" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NSI</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C218" s="15" t="n"/>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>NextEnergy Solar Ord</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>GG00BJ0JVY01</t>
+        </is>
+      </c>
+      <c r="C218" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NESF</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C219" s="15" t="n"/>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Nippon Active Value Ord</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>GB00BKLGLS10</t>
+        </is>
+      </c>
+      <c r="C219" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NAVF</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C220" s="15" t="n"/>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>North Atlantic Smaller Cos Ord</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>GB00BRDXZ870</t>
+        </is>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NAS</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C221" s="15" t="n"/>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Northern 2 VCT Ord</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>GB0005356430</t>
+        </is>
+      </c>
+      <c r="C221" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NTV</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C222" s="15" t="n"/>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Northern 3 VCT Ord</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>GB0031152027</t>
+        </is>
+      </c>
+      <c r="C222" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NTN</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C223" s="15" t="n"/>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Northern Venture Trust Ord</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>GB0006450703</t>
+        </is>
+      </c>
+      <c r="C223" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NVT</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C224" s="15" t="n"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Oakley Capital Investments Ord</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BMG670131058</t>
+        </is>
+      </c>
+      <c r="C224" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OCI</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C225" s="15" t="n"/>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oberon AIM VCT Ord</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>GB00B1SN3863</t>
+        </is>
+      </c>
+      <c r="C225" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OVCT</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C226" s="15" t="n"/>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Octopus AIM VCT Ord</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>GB0034202076</t>
+        </is>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OOA</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C227" s="15" t="n"/>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Octopus AIM VCT 2</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>GB00B0JQZZ80</t>
+        </is>
+      </c>
+      <c r="C227" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OSEC</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C228" s="15" t="n"/>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Octopus Apollo VCT Ord</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>GB00B17B3479</t>
+        </is>
+      </c>
+      <c r="C228" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OAP3</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C229" s="15" t="n"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Octopus Future Generations VCT Ord</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>GB00BNGFHX14</t>
+        </is>
+      </c>
+      <c r="C229" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OFG</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C230" s="15" t="n"/>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Octopus Renewables Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>GB00BJM02935</t>
+        </is>
+      </c>
+      <c r="C230" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ORIT</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C231" s="15" t="n"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Octopus Titan VCT Ord</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>GB00B28V9347</t>
+        </is>
+      </c>
+      <c r="C231" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OTV2</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C232" s="15" t="n"/>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Odyssean Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>GB00BFFK7H57</t>
+        </is>
+      </c>
+      <c r="C232" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OIT</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C233" s="15" t="n"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Onward Opportunities Ltd</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>GG00BMZR1514</t>
+        </is>
+      </c>
+      <c r="C233" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ONWD</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C234" s="15" t="n"/>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Oryx International Growth Ord</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>GG00B3BTVQ94</t>
+        </is>
+      </c>
+      <c r="C234" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OIG</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C235" s="15" t="n"/>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Oxford Technology VCT 2 Ord</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>GB0003105052</t>
+        </is>
+      </c>
+      <c r="C235" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OXH</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C236" s="15" t="n"/>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Oxford Technology VCT 3 Ord</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>GB00BN73FN07</t>
+        </is>
+      </c>
+      <c r="C236" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OT3</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C237" s="15" t="n"/>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Oxford Technology VCT 4 Ord</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>GB00BN73FP21</t>
+        </is>
+      </c>
+      <c r="C237" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OT4</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C238" s="15" t="n"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Oxford Technology VCT Ord</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>GB00BN73FM99</t>
+        </is>
+      </c>
+      <c r="C238" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:OT1</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C239" s="15" t="n"/>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Pacific Assets Ord</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>GB0006674385</t>
+        </is>
+      </c>
+      <c r="C239" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PAC</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C240" s="15" t="n"/>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Pacific Horizon Ord</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>GB0006667470</t>
+        </is>
+      </c>
+      <c r="C240" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PHI</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C241" s="15" t="n"/>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Pantheon Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>GB00BLNNFL88</t>
+        </is>
+      </c>
+      <c r="C241" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PINT</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C242" s="15" t="n"/>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Pantheon International Ord</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>GB00BP37WF17</t>
+        </is>
+      </c>
+      <c r="C242" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PIN</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C243" s="15" t="n"/>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Partners Group Private Equity Ord</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>GG00B28C2R28</t>
+        </is>
+      </c>
+      <c r="C243" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PEY</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C244" s="15" t="n"/>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Patria Private Equity Trust</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>GB0030474687</t>
+        </is>
+      </c>
+      <c r="C244" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PPET</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C245" s="15" t="n"/>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Pembroke VCT B</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>GB00BQVC9S79</t>
+        </is>
+      </c>
+      <c r="C245" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PEMB</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C246" s="15" t="n"/>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Pershing Square Holdings Ord</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>GG00BPFJTF46</t>
+        </is>
+      </c>
+      <c r="C246" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PSH</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C247" s="15" t="n"/>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Personal Assets Ord</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>GB00BM8B5H06</t>
+        </is>
+      </c>
+      <c r="C247" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PNL</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C248" s="15" t="n"/>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Phoenix Digital Assets Ord</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>GB00BMW34204</t>
+        </is>
+      </c>
+      <c r="C248" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/AQSE:PNIX</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C249" s="15" t="n"/>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Phoenix Spree Deutschland Ord</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>JE00B248KJ21</t>
+        </is>
+      </c>
+      <c r="C249" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PSDL</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C250" s="15" t="n"/>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Polar Capital Global Financials Ord</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>GB00B9XQT119</t>
+        </is>
+      </c>
+      <c r="C250" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PCFT</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C251" s="15" t="n"/>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Polar Capital Glb Healthcare Ord</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>GB00B6832P16</t>
+        </is>
+      </c>
+      <c r="C251" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PCGH</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C252" s="15" t="n"/>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Polar Capital Technology Ord</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>GB00BR3YV268</t>
+        </is>
+      </c>
+      <c r="C252" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PCT</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C253" s="15" t="n"/>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Praetura Growth VCT Ord</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>GB00BL690L89</t>
+        </is>
+      </c>
+      <c r="C253" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PGV</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C254" s="15" t="n"/>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ProVen Growth and Income VCT Ord</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>GB00B5B7YS03</t>
+        </is>
+      </c>
+      <c r="C254" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PGOO</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C255" s="15" t="n"/>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ProVen VCT Ord</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>GB00B8GH9P84</t>
+        </is>
+      </c>
+      <c r="C255" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PVN</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C256" s="15" t="n"/>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Puma AIM VCT Ord</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>GB00BRC89928</t>
+        </is>
+      </c>
+      <c r="C256" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PAIM</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C257" s="15" t="n"/>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Puma Alpha VCT Ord</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>GB00BGMG7F10</t>
+        </is>
+      </c>
+      <c r="C257" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PUAL</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C258" s="15" t="n"/>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Puma VCT 13 Ord</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>GB00BD5B1L68</t>
+        </is>
+      </c>
+      <c r="C258" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:PU13</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C259" s="15" t="n"/>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Real Estate Credit Investments Ord</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>GB00B0HW5366</t>
+        </is>
+      </c>
+      <c r="C259" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RECI</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C260" s="15" t="n"/>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Regional REIT Ord</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>GG00BSY2LD72</t>
+        </is>
+      </c>
+      <c r="C260" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RGL</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C261" s="15" t="n"/>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Residential Secure Income Ord</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>GB00BYSX1508</t>
+        </is>
+      </c>
+      <c r="C261" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RESI</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C262" s="15" t="n"/>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Rights &amp; Issues Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>GB0007392078</t>
+        </is>
+      </c>
+      <c r="C262" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RIII</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C263" s="15" t="n"/>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>RIT Capital Partners Ord</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>GB0007366395</t>
+        </is>
+      </c>
+      <c r="C263" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RCP</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C264" s="15" t="n"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>River UK Micro Cap Ord</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>GG00BNDMJP11</t>
+        </is>
+      </c>
+      <c r="C264" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RMMC</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C265" s="15" t="n"/>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Riverstone Credit Opportunities Income</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>GB00BRBWLX34</t>
+        </is>
+      </c>
+      <c r="C265" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RCOI</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C266" s="15" t="n"/>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Riverstone Energy Ord</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>GG00BSNRFW06</t>
+        </is>
+      </c>
+      <c r="C266" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RSE</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C267" s="15" t="n"/>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>RM Infrastructure Income Ord</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>GB00BYMTBG55</t>
+        </is>
+      </c>
+      <c r="C267" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RMII</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C268" s="15" t="n"/>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Rockwood Strategic Ord</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>GB00BRRD5L66</t>
+        </is>
+      </c>
+      <c r="C268" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RKW</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C269" s="15" t="n"/>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>RTW Biotech Opportunities Ord</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>GG00BKTRRM22</t>
+        </is>
+      </c>
+      <c r="C269" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RTW</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C270" s="15" t="n"/>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Ruffer Investment Company</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>GB00B018CS46</t>
+        </is>
+      </c>
+      <c r="C270" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:RICA</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C271" s="15" t="n"/>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Schiehallion Fund Ord</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>GG00BJ0CDD21</t>
+        </is>
+      </c>
+      <c r="C271" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MNTN</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C272" s="15" t="n"/>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Schroder Asian Total Return Inv. Company</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>GB0008710799</t>
+        </is>
+      </c>
+      <c r="C272" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ATR</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C273" s="15" t="n"/>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Schroder AsiaPacific Ord</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>GB0007918872</t>
+        </is>
+      </c>
+      <c r="C273" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SDP</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C274" s="15" t="n"/>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Schroder British Opportunities Ord</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>GB00BN7JZR28</t>
+        </is>
+      </c>
+      <c r="C274" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SBO</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C275" s="15" t="n"/>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Schroder BSC Social Impact Trust Ord</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>GB00BF781319</t>
+        </is>
+      </c>
+      <c r="C275" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SBSI</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C276" s="15" t="n"/>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Schroder European Real Estate Inv Trust</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>GB00BY7R8K77</t>
+        </is>
+      </c>
+      <c r="C276" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SERE</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C277" s="15" t="n"/>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Schroder Income Growth Ord</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>GB0007915860</t>
+        </is>
+      </c>
+      <c r="C277" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SCF</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C278" s="15" t="n"/>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Schroder Japan Trust Ord</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>GB0008022849</t>
+        </is>
+      </c>
+      <c r="C278" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SJG</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C279" s="15" t="n"/>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Schroder Oriental Income Ord</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>GB00B0CRWN59</t>
+        </is>
+      </c>
+      <c r="C279" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SOI</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C280" s="15" t="n"/>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Schroder Real Estate Invest Ord</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>GB00B01HM147</t>
+        </is>
+      </c>
+      <c r="C280" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SREI</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C281" s="15" t="n"/>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Schroder UK Mid Cap Ord</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>GB0006108418</t>
+        </is>
+      </c>
+      <c r="C281" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SCP</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C282" s="15" t="n"/>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Schroders Capital Global Innov Trust Ord</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>GB00BVG1CF25</t>
+        </is>
+      </c>
+      <c r="C282" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:INOV</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C283" s="15" t="n"/>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Scottish American Ord</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>GB0007873697</t>
+        </is>
+      </c>
+      <c r="C283" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SAIN</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C284" s="15" t="n"/>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Scottish Mortgage Ord</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>GB00BLDYK618</t>
+        </is>
+      </c>
+      <c r="C284" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SMT</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C285" s="15" t="n"/>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Scottish Oriental Smaller Cos Ord</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>GB00BRBL6574</t>
+        </is>
+      </c>
+      <c r="C285" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SST</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C286" s="15" t="n"/>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SDCL Efficiency Income Trust plc.</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>GB00BGHVZM47</t>
+        </is>
+      </c>
+      <c r="C286" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SEIT</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C287" s="15" t="n"/>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Seed Innovations Ord</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>GG00BRK9BQ81</t>
+        </is>
+      </c>
+      <c r="C287" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SEED</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C288" s="15" t="n"/>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Seneca Growth Capital VCT</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>GB0031256109</t>
+        </is>
+      </c>
+      <c r="C288" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:HYG</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C289" s="15" t="n"/>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Seneca Growth Capital VCT B</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>GB00BG13MH08</t>
+        </is>
+      </c>
+      <c r="C289" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SVCT</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C290" s="15" t="n"/>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Sequoia Economic Infrastructure Inc Ord</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>GG00BV54HY67</t>
+        </is>
+      </c>
+      <c r="C290" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SEQI</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C291" s="15" t="n"/>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Seraphim Space Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>GB00BKPG0138</t>
+        </is>
+      </c>
+      <c r="C291" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SSIT</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C292" s="15" t="n"/>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Sherborne Investors (Guernsey) C Ltd</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>GG00BZ3C3B94</t>
+        </is>
+      </c>
+      <c r="C292" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SIGC</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C293" s="15" t="n"/>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Social Housing REIT Ord</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>GB00BF0P7H59</t>
+        </is>
+      </c>
+      <c r="C293" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SOHO</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C294" s="15" t="n"/>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Sprott Physical Gold and Silver Trust</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>CA85208R1010</t>
+        </is>
+      </c>
+      <c r="C294" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/ARCA:CEF</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C295" s="15" t="n"/>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Sprott Physical Gold and Silver Trust USD</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>CA85208R1010</t>
+        </is>
+      </c>
+      <c r="C295" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/TSX:CEF</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C296" s="15" t="n"/>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Sprott Physical Gold Trust</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CA85207H1047</t>
+        </is>
+      </c>
+      <c r="C296" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/ARCA:PHYS</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C297" s="15" t="n"/>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Sprott Physical Silver Trust</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CA85207K1075</t>
+        </is>
+      </c>
+      <c r="C297" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/ARCA:PSLV</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C298" s="15" t="n"/>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Strategic Equity Capital Ord</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>GB00B0BDCB21</t>
+        </is>
+      </c>
+      <c r="C298" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SEC</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C299" s="15" t="n"/>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>STS Global Income &amp; Growth Trust Ord</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>GB00B09G3N23</t>
+        </is>
+      </c>
+      <c r="C299" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:STS</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C300" s="15" t="n"/>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Sure Ventures Ord</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>GB00BYWYZ460</t>
+        </is>
+      </c>
+      <c r="C300" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SURE</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C301" s="15" t="n"/>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Symphony International Holding Ord</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>VGG548121059</t>
+        </is>
+      </c>
+      <c r="C301" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SIHL</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C302" s="15" t="n"/>
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Syncona Ord</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>GG00B8P59C08</t>
+        </is>
+      </c>
+      <c r="C302" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SYNC</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C303" s="15" t="n"/>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Target Healthcare REIT Ord</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>GB00BJGTLF51</t>
+        </is>
+      </c>
+      <c r="C303" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:THRL</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C304" s="15" t="n"/>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Temple Bar Ord</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>GB00BMV92D64</t>
+        </is>
+      </c>
+      <c r="C304" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TMPL</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C305" s="15" t="n"/>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Templeton Emerging Mkts Invmt Tr TEMIT</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>GB00BKPG0S09</t>
+        </is>
+      </c>
+      <c r="C305" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TEM</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C306" s="15" t="n"/>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Tetragon Financial Ord</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>GG00B1RMC548</t>
+        </is>
+      </c>
+      <c r="C306" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/XAMS:TFG</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C307" s="15" t="n"/>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Tetragon Financial Ord USD</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>GG00B1RMC548</t>
+        </is>
+      </c>
+      <c r="C307" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TFG</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C308" s="15" t="n"/>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Tetragon Financial Ord USD</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>GG00B1RMC548</t>
+        </is>
+      </c>
+      <c r="C308" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/CEUX:TFGa</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C309" s="15" t="n"/>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Biotech Growth Ord</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>GB0000385517</t>
+        </is>
+      </c>
+      <c r="C309" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BIOG</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C310" s="15" t="n"/>
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>City of London Ord</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>GB0001990497</t>
+        </is>
+      </c>
+      <c r="C310" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:CTY</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C311" s="15" t="n"/>
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>The European Smaller Companies Trust PLC</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>GB00BMCF8689</t>
+        </is>
+      </c>
+      <c r="C311" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ESCT</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="18" customFormat="1" customHeight="1" s="10">
-      <c r="C312" s="15" t="n"/>
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>The Global Smaller Companies Trust Ord</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>GB00BKLXD974</t>
+        </is>
+      </c>
+      <c r="C312" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:GSCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Merchants Trust Ord</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>GB0005800072</t>
+        </is>
+      </c>
+      <c r="C313" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:MRCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>North American Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>GB00BJ00Z303</t>
+        </is>
+      </c>
+      <c r="C314" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:NAIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Renewables Infrastructure Grp</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>GG00BBHX2H91</t>
+        </is>
+      </c>
+      <c r="C315" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TRIG</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Tiger Alpha Ord</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>GB00BTY5RC40</t>
+        </is>
+      </c>
+      <c r="C316" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Tooru Ord</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>GB00BKKD0862</t>
+        </is>
+      </c>
+      <c r="C317" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TOO</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>TR Property Ord</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>GB0009064097</t>
+        </is>
+      </c>
+      <c r="C318" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Triple Point Venture VCT</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>GB00BDTYGZ09</t>
+        </is>
+      </c>
+      <c r="C319" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Tritax Big Box Ord</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>GB00BG49KP99</t>
+        </is>
+      </c>
+      <c r="C320" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:BBOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Tufton Assets Ord</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>GG00BSFVPB94</t>
+        </is>
+      </c>
+      <c r="C321" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>TwentyFour Income Ord</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>GG00B90J5Z95</t>
+        </is>
+      </c>
+      <c r="C322" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:TFIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>TwentyFour Select Monthly Income Ord</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>GG00BJVDZ946</t>
+        </is>
+      </c>
+      <c r="C323" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:SMIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>UIL Ord</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>BMG917071026</t>
+        </is>
+      </c>
+      <c r="C324" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:UTL</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>UIL ZDP 2026</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>BMG916101402</t>
+        </is>
+      </c>
+      <c r="C325" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:UTLH</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>UIL ZDP 2028</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>BMG916101576</t>
+        </is>
+      </c>
+      <c r="C326" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:UTLI</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Unicorn AIM VCT Ord</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>GB00B1RTFN43</t>
+        </is>
+      </c>
+      <c r="C327" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:UAV</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>US Solar Fund Ord</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>GB00BJCWFX49</t>
+        </is>
+      </c>
+      <c r="C328" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:USF</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Utilico Emerging Markets Ord</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>GB00BD45S967</t>
+        </is>
+      </c>
+      <c r="C329" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:UEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Value and Indexed Property Income Ord</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>GB0008484718</t>
+        </is>
+      </c>
+      <c r="C330" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>VH Global Energy Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>GB00BNKVP754</t>
+        </is>
+      </c>
+      <c r="C331" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:ENRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Vietnam Enterprise Ord</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>KYG9361H1092</t>
+        </is>
+      </c>
+      <c r="C332" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:VEIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>VietNam Holding Ord</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>GG00BJQZ9H10</t>
+        </is>
+      </c>
+      <c r="C333" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:VNH</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>VinaCapital Vietnam Opp Fund Ord</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>GG00BYXVT888</t>
+        </is>
+      </c>
+      <c r="C334" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:VOF</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Volta Finance Ord EUR</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>GG00B1GHHH78</t>
+        </is>
+      </c>
+      <c r="C335" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:VTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>VPC Specialty Lending Investments Ord</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>GB00BVG6X439</t>
+        </is>
+      </c>
+      <c r="C336" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:VSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Worldwide Healthcare Ord</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>GB00BN455J50</t>
+        </is>
+      </c>
+      <c r="C337" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:WWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Worsley Investors Ord</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>GG00BHXH0C87</t>
+        </is>
+      </c>
+      <c r="C338" s="14" t="inlineStr">
+        <is>
+          <t>https://www.ajbell.co.uk/market-research/LSE:WINV</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" display="https://www.ajbell.co.uk/market-research/LSE:III" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="https://www.ajbell.co.uk/market-research/LSE:ANII" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="https://www.ajbell.co.uk/market-research/LSE:ASLI" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" display="https://www.ajbell.co.uk/market-research/LSE:AOF" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" display="https://www.ajbell.co.uk/market-research/LSE:ALNA" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" display="https://www.ajbell.co.uk/market-research/LSE:AA4" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" display="https://www.ajbell.co.uk/market-research/LSE:AIE" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" display="https://www.ajbell.co.uk/market-research/LSE:AGT" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" display="https://www.ajbell.co.uk/market-research/LSE:BGS" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
@@ -2389,6 +6485,293 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId337"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
